--- a/app/src/main/assets/roster_template.xlsx
+++ b/app/src/main/assets/roster_template.xlsx
@@ -12,9 +12,10 @@
   <cols>
     <col min="1" max="1" width="16"/>
     <col min="2" max="2" width="10"/>
-    <col min="3" max="3" width="14"/>
-    <col min="4" max="4" width="14"/>
-    <col min="5" max="5" width="26"/>
+    <col min="3" max="3" width="8"/>
+    <col min="4" max="4" width="12"/>
+    <col min="5" max="5" width="12"/>
+    <col min="6" max="6" width="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -25,20 +26,25 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">number</t>
+          <t xml:space="preserve">gender</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">initial_class</t>
+          <t xml:space="preserve">number</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t xml:space="preserve">initial_class</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t xml:space="preserve">class_status</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t xml:space="preserve">full_name</t>
         </is>
@@ -52,20 +58,25 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">female</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.0</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1.0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t xml:space="preserve">C</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t xml:space="preserve">VINCI, Sarah</t>
         </is>
@@ -79,20 +90,25 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">female</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t xml:space="preserve">3.5</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t xml:space="preserve">GOMEZ, Maria</t>
         </is>
@@ -101,27 +117,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Australia</t>
+          <t xml:space="preserve">Argentina</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">male</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.0</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">R</t>
+          <t xml:space="preserve">4.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SMITH, Jane</t>
+          <t xml:space="preserve">R-FRD</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PEREZ, Juan</t>
         </is>
       </c>
     </row>
@@ -133,22 +154,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">female</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.0</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">C</t>
+          <t xml:space="preserve">2.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">BROWN, Emily</t>
+          <t xml:space="preserve">R-NÃO</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SMITH, Jane</t>
         </is>
       </c>
     </row>

--- a/app/src/main/assets/roster_template.xlsx
+++ b/app/src/main/assets/roster_template.xlsx
@@ -7,12 +7,53 @@
 </workbook>
 </file>
 
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+  </fonts>
+  <fills count="2">
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+  </fills>
+  <borders count="1">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+  </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
+  <dxfs count="0"/>
+</styleSheet>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="16"/>
     <col min="2" max="2" width="10"/>
-    <col min="3" max="3" width="8"/>
+    <col min="3" max="3" width="8" style="1"/>
     <col min="4" max="4" width="12"/>
     <col min="5" max="5" width="12"/>
     <col min="6" max="6" width="26"/>
@@ -29,7 +70,7 @@
           <t xml:space="preserve">gender</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">number</t>
         </is>
@@ -61,7 +102,7 @@
           <t xml:space="preserve">female</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
@@ -93,7 +134,7 @@
           <t xml:space="preserve">female</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
@@ -125,7 +166,7 @@
           <t xml:space="preserve">male</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
@@ -157,7 +198,7 @@
           <t xml:space="preserve">female</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
